--- a/artfynd/A 15808-2025 artfynd.xlsx
+++ b/artfynd/A 15808-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123973219</v>
+        <v>123973348</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>96960</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,49 +691,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>kungs1, Sm</t>
+          <t>mattlummer1, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576784</v>
+        <v>576898</v>
       </c>
       <c r="R2" t="n">
-        <v>6376723</v>
+        <v>6376580</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,19 +760,9 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,6 +771,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123973348</v>
+        <v>123973375</v>
       </c>
       <c r="B3" t="n">
-        <v>97372</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,46 +806,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>mattlummer1, Sm</t>
+          <t>kungs2, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576898</v>
+        <v>576951</v>
       </c>
       <c r="R3" t="n">
-        <v>6376580</v>
+        <v>6376635</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,9 +875,19 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +896,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1030,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123973375</v>
+        <v>123973219</v>
       </c>
       <c r="B5" t="n">
         <v>57861</v>
@@ -1078,17 +1078,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>kungs2, Sm</t>
+          <t>kungs1, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576951</v>
+        <v>576784</v>
       </c>
       <c r="R5" t="n">
-        <v>6376635</v>
+        <v>6376723</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 15808-2025 artfynd.xlsx
+++ b/artfynd/A 15808-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123973348</v>
+        <v>123973413</v>
       </c>
       <c r="B2" t="n">
-        <v>96960</v>
+        <v>58349</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>208250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,24 +713,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>mattlummer1, Sm</t>
+          <t>grod1, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576898</v>
+        <v>576986</v>
       </c>
       <c r="R2" t="n">
-        <v>6376580</v>
+        <v>6376576</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -790,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123973375</v>
+        <v>123973348</v>
       </c>
       <c r="B3" t="n">
-        <v>57861</v>
+        <v>96960</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,46 +807,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>kungs2, Sm</t>
+          <t>mattlummer1, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576951</v>
+        <v>576898</v>
       </c>
       <c r="R3" t="n">
-        <v>6376635</v>
+        <v>6376580</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,19 +876,9 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,6 +887,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -914,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123973413</v>
+        <v>123973375</v>
       </c>
       <c r="B4" t="n">
-        <v>58349</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,21 +922,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208250</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -952,7 +944,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -963,14 +954,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>grod1, Sm</t>
+          <t>kungs2, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576986</v>
+        <v>576951</v>
       </c>
       <c r="R4" t="n">
-        <v>6376576</v>
+        <v>6376635</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,9 +991,19 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1012,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15808-2025 artfynd.xlsx
+++ b/artfynd/A 15808-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123973413</v>
+        <v>123973348</v>
       </c>
       <c r="B2" t="n">
-        <v>58349</v>
+        <v>96960</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208250</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,25 +713,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>grod1, Sm</t>
+          <t>mattlummer1, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576986</v>
+        <v>576898</v>
       </c>
       <c r="R2" t="n">
-        <v>6376576</v>
+        <v>6376580</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -791,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123973348</v>
+        <v>123973219</v>
       </c>
       <c r="B3" t="n">
-        <v>96960</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,49 +806,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>mattlummer1, Sm</t>
+          <t>kungs1, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576898</v>
+        <v>576784</v>
       </c>
       <c r="R3" t="n">
-        <v>6376580</v>
+        <v>6376723</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,9 +875,19 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,7 +896,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -906,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123973375</v>
+        <v>123973413</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>58349</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>208250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -944,6 +952,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -954,14 +963,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>kungs2, Sm</t>
+          <t>grod1, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576951</v>
+        <v>576986</v>
       </c>
       <c r="R4" t="n">
-        <v>6376635</v>
+        <v>6376576</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,19 +1000,9 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,6 +1011,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1030,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123973219</v>
+        <v>123973375</v>
       </c>
       <c r="B5" t="n">
         <v>57861</v>
@@ -1078,17 +1078,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>kungs1, Sm</t>
+          <t>kungs2, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576784</v>
+        <v>576951</v>
       </c>
       <c r="R5" t="n">
-        <v>6376723</v>
+        <v>6376635</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 15808-2025 artfynd.xlsx
+++ b/artfynd/A 15808-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123973219</v>
+        <v>123973413</v>
       </c>
       <c r="B3" t="n">
-        <v>57861</v>
+        <v>58349</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>208250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -828,6 +828,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -838,17 +839,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>kungs1, Sm</t>
+          <t>grod1, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576784</v>
+        <v>576986</v>
       </c>
       <c r="R3" t="n">
-        <v>6376723</v>
+        <v>6376576</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,19 +876,9 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,6 +887,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -914,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123973413</v>
+        <v>123973375</v>
       </c>
       <c r="B4" t="n">
-        <v>58349</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,21 +922,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208250</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -952,7 +944,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -963,14 +954,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>grod1, Sm</t>
+          <t>kungs2, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576986</v>
+        <v>576951</v>
       </c>
       <c r="R4" t="n">
-        <v>6376576</v>
+        <v>6376635</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,9 +991,19 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1012,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1030,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123973375</v>
+        <v>123973219</v>
       </c>
       <c r="B5" t="n">
         <v>57861</v>
@@ -1078,17 +1078,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>kungs2, Sm</t>
+          <t>kungs1, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576951</v>
+        <v>576784</v>
       </c>
       <c r="R5" t="n">
-        <v>6376635</v>
+        <v>6376723</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 15808-2025 artfynd.xlsx
+++ b/artfynd/A 15808-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123973375</v>
+        <v>123973219</v>
       </c>
       <c r="B2" t="n">
         <v>57883</v>
@@ -723,17 +723,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>kungs2, Sm</t>
+          <t>kungs1, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576951</v>
+        <v>576784</v>
       </c>
       <c r="R2" t="n">
-        <v>6376635</v>
+        <v>6376723</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1030,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123973219</v>
+        <v>123973375</v>
       </c>
       <c r="B5" t="n">
         <v>57883</v>
@@ -1078,17 +1078,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>kungs1, Sm</t>
+          <t>kungs2, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576784</v>
+        <v>576951</v>
       </c>
       <c r="R5" t="n">
-        <v>6376723</v>
+        <v>6376635</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 15808-2025 artfynd.xlsx
+++ b/artfynd/A 15808-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123973219</v>
+        <v>123973375</v>
       </c>
       <c r="B2" t="n">
         <v>57883</v>
@@ -723,17 +723,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>kungs1, Sm</t>
+          <t>kungs2, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576784</v>
+        <v>576951</v>
       </c>
       <c r="R2" t="n">
-        <v>6376723</v>
+        <v>6376635</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,17 +792,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123973348</v>
+        <v>123973219</v>
       </c>
       <c r="B3" t="n">
-        <v>96982</v>
+        <v>57883</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,49 +815,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>mattlummer1, Sm</t>
+          <t>kungs1, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576898</v>
+        <v>576784</v>
       </c>
       <c r="R3" t="n">
-        <v>6376580</v>
+        <v>6376723</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,18 +884,27 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -907,17 +916,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123973413</v>
+        <v>123973348</v>
       </c>
       <c r="B4" t="n">
-        <v>58371</v>
+        <v>96982</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,21 +939,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208250</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -952,25 +961,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>grod1, Sm</t>
+          <t>mattlummer1, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576986</v>
+        <v>576898</v>
       </c>
       <c r="R4" t="n">
-        <v>6376576</v>
+        <v>6376580</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1023,17 +1031,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123973375</v>
+        <v>123973413</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>58371</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,21 +1054,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>208250</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1068,6 +1076,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -1078,14 +1087,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>kungs2, Sm</t>
+          <t>grod1, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576951</v>
+        <v>576986</v>
       </c>
       <c r="R5" t="n">
-        <v>6376635</v>
+        <v>6376576</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1115,27 +1124,18 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15808-2025 artfynd.xlsx
+++ b/artfynd/A 15808-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123973375</v>
+        <v>123973219</v>
       </c>
       <c r="B2" t="n">
         <v>57883</v>
@@ -723,17 +723,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>kungs2, Sm</t>
+          <t>kungs1, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576951</v>
+        <v>576784</v>
       </c>
       <c r="R2" t="n">
-        <v>6376635</v>
+        <v>6376723</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,17 +792,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Moritz Moser, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123973219</v>
+        <v>123973348</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>96982</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,49 +815,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>kungs1, Sm</t>
+          <t>mattlummer1, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576784</v>
+        <v>576898</v>
       </c>
       <c r="R3" t="n">
-        <v>6376723</v>
+        <v>6376580</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,27 +884,18 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -916,17 +907,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Moritz Moser, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123973348</v>
+        <v>123973413</v>
       </c>
       <c r="B4" t="n">
-        <v>96982</v>
+        <v>58371</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>208250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -961,24 +952,25 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>mattlummer1, Sm</t>
+          <t>grod1, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576898</v>
+        <v>576986</v>
       </c>
       <c r="R4" t="n">
-        <v>6376580</v>
+        <v>6376576</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1031,17 +1023,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Moritz Moser, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123973413</v>
+        <v>123973375</v>
       </c>
       <c r="B5" t="n">
-        <v>58371</v>
+        <v>57883</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,21 +1046,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208250</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1076,7 +1068,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -1087,14 +1078,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>grod1, Sm</t>
+          <t>kungs2, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576986</v>
+        <v>576951</v>
       </c>
       <c r="R5" t="n">
-        <v>6376576</v>
+        <v>6376635</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1124,18 +1115,27 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15808-2025 artfynd.xlsx
+++ b/artfynd/A 15808-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123973219</v>
+        <v>123973348</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>96982</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,49 +691,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>kungs1, Sm</t>
+          <t>mattlummer1, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576784</v>
+        <v>576898</v>
       </c>
       <c r="R2" t="n">
-        <v>6376723</v>
+        <v>6376580</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,27 +760,18 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123973348</v>
+        <v>123973375</v>
       </c>
       <c r="B3" t="n">
-        <v>96982</v>
+        <v>57883</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,46 +806,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>mattlummer1, Sm</t>
+          <t>kungs2, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576898</v>
+        <v>576951</v>
       </c>
       <c r="R3" t="n">
-        <v>6376580</v>
+        <v>6376635</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,18 +875,27 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123973413</v>
+        <v>123973219</v>
       </c>
       <c r="B4" t="n">
-        <v>58371</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208250</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -952,7 +952,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -963,17 +962,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>grod1, Sm</t>
+          <t>kungs1, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576986</v>
+        <v>576784</v>
       </c>
       <c r="R4" t="n">
-        <v>6376576</v>
+        <v>6376723</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,18 +999,27 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1023,17 +1031,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123973375</v>
+        <v>123973413</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>58371</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,21 +1054,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>208250</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1068,6 +1076,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -1078,14 +1087,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>kungs2, Sm</t>
+          <t>grod1, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576951</v>
+        <v>576986</v>
       </c>
       <c r="R5" t="n">
-        <v>6376635</v>
+        <v>6376576</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1115,27 +1124,18 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15808-2025 artfynd.xlsx
+++ b/artfynd/A 15808-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123973375</v>
+        <v>123973413</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>58371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>208250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -828,6 +828,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -838,14 +839,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>kungs2, Sm</t>
+          <t>grod1, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576951</v>
+        <v>576986</v>
       </c>
       <c r="R3" t="n">
-        <v>6376635</v>
+        <v>6376576</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,27 +876,18 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -914,7 +906,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123973219</v>
+        <v>123973375</v>
       </c>
       <c r="B4" t="n">
         <v>57883</v>
@@ -962,17 +954,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>kungs1, Sm</t>
+          <t>kungs2, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576784</v>
+        <v>576951</v>
       </c>
       <c r="R4" t="n">
-        <v>6376723</v>
+        <v>6376635</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,17 +1023,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Moritz Moser, Anna Drenk</t>
+          <t>Anna Drenk, Moritz Moser, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123973413</v>
+        <v>123973219</v>
       </c>
       <c r="B5" t="n">
-        <v>58371</v>
+        <v>57883</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,21 +1046,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208250</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1076,7 +1068,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -1087,17 +1078,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>grod1, Sm</t>
+          <t>kungs1, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576986</v>
+        <v>576784</v>
       </c>
       <c r="R5" t="n">
-        <v>6376576</v>
+        <v>6376723</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,18 +1115,27 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 15808-2025 artfynd.xlsx
+++ b/artfynd/A 15808-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123973348</v>
+        <v>123973375</v>
       </c>
       <c r="B2" t="n">
-        <v>96982</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>mattlummer1, Sm</t>
+          <t>kungs2, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576898</v>
+        <v>576951</v>
       </c>
       <c r="R2" t="n">
-        <v>6376580</v>
+        <v>6376635</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -760,18 +760,27 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -783,7 +792,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Drenk, Moritz Moser, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Moritz Moser, Anna Drenk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -906,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123973375</v>
+        <v>123973219</v>
       </c>
       <c r="B4" t="n">
         <v>57883</v>
@@ -954,17 +963,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>kungs2, Sm</t>
+          <t>kungs1, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576951</v>
+        <v>576784</v>
       </c>
       <c r="R4" t="n">
-        <v>6376635</v>
+        <v>6376723</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123973219</v>
+        <v>123973348</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>96982</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,49 +1055,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>kungs1, Sm</t>
+          <t>mattlummer1, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576784</v>
+        <v>576898</v>
       </c>
       <c r="R5" t="n">
-        <v>6376723</v>
+        <v>6376580</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,27 +1124,18 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
